--- a/memory_master.xlsx
+++ b/memory_master.xlsx
@@ -18366,7 +18366,7 @@
       </c>
       <c r="AA123" s="14" t="inlineStr">
         <is>
-          <t>PROCESSING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB123" s="14" t="inlineStr">
@@ -18376,7 +18376,7 @@
       </c>
       <c r="AC123" s="14" t="inlineStr">
         <is>
-          <t>画像生成処理中</t>
+          <t>生成完了：122.webp</t>
         </is>
       </c>
     </row>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="AA124" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB124" s="14" t="inlineStr">
@@ -18519,7 +18519,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC124" s="14" t="str"/>
+      <c r="AC124" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：123.webp</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="96" customHeight="1">
       <c r="A125" s="14" t="inlineStr">
@@ -18652,7 +18656,7 @@
       </c>
       <c r="AA125" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB125" s="14" t="inlineStr">
@@ -18660,7 +18664,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC125" s="14" t="str"/>
+      <c r="AC125" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：124.webp</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="96" customHeight="1">
       <c r="A126" s="14" t="inlineStr">
@@ -18793,7 +18801,7 @@
       </c>
       <c r="AA126" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB126" s="14" t="inlineStr">
@@ -18801,7 +18809,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC126" s="14" t="str"/>
+      <c r="AC126" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：125.webp</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="96" customHeight="1">
       <c r="A127" s="14" t="inlineStr">
@@ -18934,7 +18946,7 @@
       </c>
       <c r="AA127" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB127" s="14" t="inlineStr">
@@ -18942,7 +18954,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC127" s="14" t="str"/>
+      <c r="AC127" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：126.webp</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="96" customHeight="1">
       <c r="A128" s="14" t="inlineStr">
@@ -19075,7 +19091,7 @@
       </c>
       <c r="AA128" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB128" s="14" t="inlineStr">
@@ -19083,7 +19099,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC128" s="14" t="str"/>
+      <c r="AC128" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：127.webp</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="96" customHeight="1">
       <c r="A129" s="14" t="inlineStr">
@@ -19220,7 +19240,7 @@
       </c>
       <c r="AA129" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB129" s="14" t="inlineStr">
@@ -19228,7 +19248,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC129" s="14" t="str"/>
+      <c r="AC129" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：128.webp</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="96" customHeight="1">
       <c r="A130" s="14" t="inlineStr">
@@ -19361,7 +19385,7 @@
       </c>
       <c r="AA130" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB130" s="14" t="inlineStr">
@@ -19369,7 +19393,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC130" s="14" t="str"/>
+      <c r="AC130" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：129.webp</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="96" customHeight="1">
       <c r="A131" s="14" t="inlineStr">
@@ -19502,7 +19530,7 @@
       </c>
       <c r="AA131" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB131" s="14" t="inlineStr">
@@ -19510,7 +19538,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC131" s="14" t="str"/>
+      <c r="AC131" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：130.webp</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="96" customHeight="1">
       <c r="A132" s="14" t="inlineStr">
@@ -19643,7 +19675,7 @@
       </c>
       <c r="AA132" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB132" s="14" t="inlineStr">
@@ -19651,7 +19683,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC132" s="14" t="str"/>
+      <c r="AC132" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：131.webp</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="96" customHeight="1">
       <c r="A133" s="14" t="inlineStr">
@@ -19784,7 +19820,7 @@
       </c>
       <c r="AA133" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB133" s="14" t="inlineStr">
@@ -19792,7 +19828,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC133" s="14" t="str"/>
+      <c r="AC133" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：132.webp</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="96" customHeight="1">
       <c r="A134" s="14" t="inlineStr">
@@ -19925,7 +19965,7 @@
       </c>
       <c r="AA134" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB134" s="14" t="inlineStr">
@@ -19933,7 +19973,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC134" s="14" t="str"/>
+      <c r="AC134" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：133.webp</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="96" customHeight="1">
       <c r="A135" s="14" t="inlineStr">
@@ -20066,7 +20110,7 @@
       </c>
       <c r="AA135" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB135" s="14" t="inlineStr">
@@ -20074,7 +20118,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC135" s="14" t="str"/>
+      <c r="AC135" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：134.webp</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="96" customHeight="1">
       <c r="A136" s="14" t="inlineStr">
@@ -20207,7 +20255,7 @@
       </c>
       <c r="AA136" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB136" s="14" t="inlineStr">
@@ -20215,7 +20263,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC136" s="14" t="str"/>
+      <c r="AC136" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：135.webp</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="96" customHeight="1">
       <c r="A137" s="14" t="inlineStr">
@@ -20348,7 +20400,7 @@
       </c>
       <c r="AA137" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB137" s="14" t="inlineStr">
@@ -20356,7 +20408,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC137" s="14" t="str"/>
+      <c r="AC137" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：136.webp</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="96" customHeight="1">
       <c r="A138" s="14" t="inlineStr">
@@ -20489,7 +20545,7 @@
       </c>
       <c r="AA138" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PROCESSING</t>
         </is>
       </c>
       <c r="AB138" s="14" t="inlineStr">
@@ -20497,7 +20553,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC138" s="14" t="str"/>
+      <c r="AC138" s="14" t="inlineStr">
+        <is>
+          <t>画像生成処理中</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="96" customHeight="1">
       <c r="A139" s="14" t="inlineStr">

--- a/memory_master.xlsx
+++ b/memory_master.xlsx
@@ -20545,7 +20545,7 @@
       </c>
       <c r="AA138" s="14" t="inlineStr">
         <is>
-          <t>PROCESSING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB138" s="14" t="inlineStr">
@@ -20555,7 +20555,7 @@
       </c>
       <c r="AC138" s="14" t="inlineStr">
         <is>
-          <t>画像生成処理中</t>
+          <t>生成完了：137.webp</t>
         </is>
       </c>
     </row>
@@ -20690,7 +20690,7 @@
       </c>
       <c r="AA139" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB139" s="14" t="inlineStr">
@@ -20698,7 +20698,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC139" s="14" t="str"/>
+      <c r="AC139" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：138.webp</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="96" customHeight="1">
       <c r="A140" s="14" t="inlineStr">
@@ -20831,7 +20835,7 @@
       </c>
       <c r="AA140" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB140" s="14" t="inlineStr">
@@ -20839,7 +20843,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC140" s="14" t="str"/>
+      <c r="AC140" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：139.webp</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="96" customHeight="1">
       <c r="A141" s="14" t="inlineStr">
@@ -20972,7 +20980,7 @@
       </c>
       <c r="AA141" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB141" s="14" t="inlineStr">
@@ -20980,7 +20988,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC141" s="14" t="str"/>
+      <c r="AC141" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：140.webp</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="96" customHeight="1">
       <c r="A142" s="14" t="inlineStr">
@@ -21113,7 +21125,7 @@
       </c>
       <c r="AA142" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB142" s="14" t="inlineStr">
@@ -21121,7 +21133,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC142" s="14" t="str"/>
+      <c r="AC142" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：141.webp</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="96" customHeight="1">
       <c r="A143" s="14" t="inlineStr">
@@ -21254,7 +21270,7 @@
       </c>
       <c r="AA143" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB143" s="14" t="inlineStr">
@@ -21262,7 +21278,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC143" s="14" t="str"/>
+      <c r="AC143" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：142.webp</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="96" customHeight="1">
       <c r="A144" s="14" t="inlineStr">
@@ -21395,7 +21415,7 @@
       </c>
       <c r="AA144" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB144" s="14" t="inlineStr">
@@ -21403,7 +21423,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC144" s="14" t="str"/>
+      <c r="AC144" s="14" t="inlineStr">
+        <is>
+          <t>生成完了：143.webp</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="96" customHeight="1">
       <c r="A145" s="14" t="inlineStr">
@@ -21540,7 +21564,7 @@
       </c>
       <c r="AA145" s="14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PROCESSING</t>
         </is>
       </c>
       <c r="AB145" s="14" t="inlineStr">
@@ -21548,7 +21572,11 @@
           <t>UNREVIEWED</t>
         </is>
       </c>
-      <c r="AC145" s="14" t="str"/>
+      <c r="AC145" s="14" t="inlineStr">
+        <is>
+          <t>画像生成処理中</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U145">

--- a/memory_master.xlsx
+++ b/memory_master.xlsx
@@ -21564,7 +21564,7 @@
       </c>
       <c r="AA145" s="14" t="inlineStr">
         <is>
-          <t>PROCESSING</t>
+          <t>GENERATED</t>
         </is>
       </c>
       <c r="AB145" s="14" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="AC145" s="14" t="inlineStr">
         <is>
-          <t>画像生成処理中</t>
+          <t>生成完了：144.webp</t>
         </is>
       </c>
     </row>
